--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="61" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-06</t>
+          <t>Views_2026-09-07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-07</t>
+          <t>Views_2026-09-08</t>
         </is>
       </c>
     </row>
@@ -497,83 +497,46 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>512</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>516</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-vU8JsRIpLA</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Disrespected? Use the 3-Second Stoic Rule (Marcus Aurelius)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-vU8JsRIpLA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>512</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>103</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>615</t>
+          <t>516</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-07</t>
+          <t>Views_2026-09-08</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-08</t>
+          <t>Views_2026-09-09</t>
         </is>
       </c>
     </row>
@@ -497,46 +497,83 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>516</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>518</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>516</t>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>615</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-08</t>
+          <t>Views_2026-09-09</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-09</t>
+          <t>Views_2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,34 +502,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,41 +539,226 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>129</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>130</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>bJKZPpJh1pI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The Moment You STOP, They Take Control</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3XX_s7f_zbk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>When They Ask "Are You Sure?" — Do This</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>q8sgDwcuE0A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>You OFFER First, So They Stop ASKING</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5IXlofJxEUg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>When Someone Ignores You, Walk Away With Dignity (Stoic Guide)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5IXlofJxEUg</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>615</t>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1,077</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1,085</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,49 +465,49 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-09</t>
+          <t>Views_2026-09-10</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-10</t>
+          <t>Views_2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>_qmVTMUQSDg</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>519</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>523</t>
         </is>
       </c>
     </row>
@@ -539,226 +539,41 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>649</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>182</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3XX_s7f_zbk</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>When They Ask "Are You Sure?" — Do This</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>q8sgDwcuE0A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>You OFFER First, So They Stop ASKING</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>5IXlofJxEUg</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>When Someone Ignores You, Walk Away With Dignity (Stoic Guide)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5IXlofJxEUg</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1,077</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1,085</t>
+          <t>654</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-10</t>
+          <t>Views_2026-09-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-11</t>
+          <t>Views_2026-09-12</t>
         </is>
       </c>
     </row>
@@ -497,39 +497,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>523</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>525</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>181</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>703</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>706</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-11</t>
+          <t>Views_2026-09-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-12</t>
+          <t>Views_2026-09-13</t>
         </is>
       </c>
     </row>
@@ -497,83 +497,46 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>525</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>530</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>525</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>181</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>706</t>
+          <t>530</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-12</t>
+          <t>Views_2026-09-13</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-13</t>
+          <t>Views_2026-09-14</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>530</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>531</t>
         </is>
       </c>
     </row>
@@ -526,17 +526,17 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>530</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>531</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-13</t>
+          <t>Views_2026-09-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-14</t>
+          <t>Views_2026-09-15</t>
         </is>
       </c>
     </row>
@@ -497,46 +497,83 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>531</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>535</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>531</t>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>683</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-14</t>
+          <t>Views_2026-09-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-15</t>
+          <t>Views_2026-09-16</t>
         </is>
       </c>
     </row>
@@ -502,34 +502,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>535</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>539</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>98</t>
         </is>
       </c>
     </row>
@@ -568,12 +568,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>632</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>637</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-15</t>
+          <t>Views_2026-09-16</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-16</t>
+          <t>Views_2026-09-17</t>
         </is>
       </c>
     </row>
@@ -497,39 +497,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>539</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>544</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,41 +539,226 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>182</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>_FYXew5E_Xk</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>zOkGHnsmORY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3,114</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3,115</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>637</t>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4,497</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4,508</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-16</t>
+          <t>Views_2026-09-17</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-17</t>
+          <t>Views_2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>182</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>183</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>149</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>150</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,34 +576,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>544</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>545</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,152 +613,41 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>3,115</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>3,116</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>3,990</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>149</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2OilqvW_HzY</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>zOkGHnsmORY</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>3,114</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>3,115</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>4,497</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>4,508</t>
+          <t>3,994</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,189 +465,115 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-17</t>
+          <t>Views_2026-09-18</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-18</t>
+          <t>Views_2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>154</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>545</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>548</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>695</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>545</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>zOkGHnsmORY</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3,115</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>3,116</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>3,990</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3,994</t>
+          <t>702</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,115 +465,78 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-18</t>
+          <t>Views_2026-09-19</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-19</t>
+          <t>Views_2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>548</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>549</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>548</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>548</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>702</t>
+          <t>549</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-19</t>
+          <t>Views_2026-09-20</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-20</t>
+          <t>Views_2026-09-22</t>
         </is>
       </c>
     </row>
@@ -497,46 +497,83 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>549</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>552</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>cNyqLV3GFq8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>The More You Explain Your NO, The Less They Respect It</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>549</t>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>592</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-20</t>
+          <t>Views_2026-09-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-22</t>
+          <t>Views_2026-09-24</t>
         </is>
       </c>
     </row>
@@ -497,39 +497,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>552</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>561</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cNyqLV3GFq8</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The More You Explain Your NO, The Less They Respect It</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,41 +539,115 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>129</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>130</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5IXlofJxEUg</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>When Someone Ignores You, Walk Away With Dignity (Stoic Guide)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5IXlofJxEUg</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>592</t>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>924</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-22</t>
+          <t>Views_2026-09-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-24</t>
+          <t>Views_2026-09-25</t>
         </is>
       </c>
     </row>
@@ -497,157 +497,46 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>561</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>563</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>561</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>5IXlofJxEUg</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>When Someone Ignores You, Walk Away With Dignity (Stoic Guide)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5IXlofJxEUg</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>912</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>924</t>
+          <t>563</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="69" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-24</t>
+          <t>Views_2026-09-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-25</t>
+          <t>Views_2026-09-26</t>
         </is>
       </c>
     </row>
@@ -502,41 +502,115 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>563</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>565</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AB5Tw2Yd4qE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>563</t>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>767</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="69" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-25</t>
+          <t>Views_2026-09-26</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-26</t>
+          <t>Views_2026-09-27</t>
         </is>
       </c>
     </row>
@@ -497,39 +497,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>565</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>568</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>102</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AB5Tw2Yd4qE</t>
+          <t>Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,41 +576,78 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>767</t>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>892</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-26</t>
+          <t>Views_2026-09-27</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-27</t>
+          <t>Views_2026-09-28</t>
         </is>
       </c>
     </row>
@@ -497,39 +497,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>568</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>573</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,115 +539,41 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cxx0wy3mYzA</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>How to Win People’s RESPECT Before You Say a Word</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>656</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>66</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>886</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>892</t>
+          <t>662</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-27</t>
+          <t>Views_2026-09-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-28</t>
+          <t>Views_2026-09-29</t>
         </is>
       </c>
     </row>
@@ -497,39 +497,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>573</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>575</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,41 +539,115 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>130</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>131</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>0a_DUuDQFx0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The Calm Response That Stops Rude People Fast</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>662</t>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>974</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-28</t>
+          <t>Views_2026-09-29</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-29</t>
+          <t>Views_2026-09-30</t>
         </is>
       </c>
     </row>
@@ -502,12 +502,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>575</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>577</t>
         </is>
       </c>
     </row>
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>132</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0a_DUuDQFx0</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,34 +576,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>qUd0X0Wn4-s</t>
+          <t>TH331d5OGVs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
+          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>849</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>854</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-29</t>
+          <t>Views_2026-09-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-30</t>
+          <t>Views_2026-10-01</t>
         </is>
       </c>
     </row>
@@ -502,152 +502,41 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>577</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>579</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>577</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>132</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>lIx_B-vwa8g</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TH331d5OGVs</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>849</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>854</t>
+          <t>579</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-30</t>
+          <t>Views_2026-10-01</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-01</t>
+          <t>Views_2026-10-02</t>
         </is>
       </c>
     </row>
@@ -497,46 +497,83 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>579</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>582</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>579</t>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>873</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,115 +465,189 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-01</t>
+          <t>Views_2026-10-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-02</t>
+          <t>Views_2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>156</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>158</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>582</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>584</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>873</t>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1,210</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1,216</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,189 +465,78 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-02</t>
+          <t>Views_2026-10-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-03</t>
+          <t>Views_2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>584</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>585</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>584</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>584</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>agifyuQrXW8</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1,210</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1,216</t>
+          <t>585</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-03</t>
+          <t>Views_2026-10-04</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-04</t>
+          <t>Views_2026-10-06</t>
         </is>
       </c>
     </row>
@@ -497,46 +497,157 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>585</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>592</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>ZervEMzTJp8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9M1kjkk6oG8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>585</t>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1,860</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1,870</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="69" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-04</t>
+          <t>Views_2026-10-06</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-06</t>
+          <t>Views_2026-10-07</t>
         </is>
       </c>
     </row>
@@ -497,39 +497,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>592</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>598</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ZervEMzTJp8</t>
+          <t>AB5Tw2Yd4qE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Second You Explain Your NO, It Stops Being One</t>
+          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,115 +539,41 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>639</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>402</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>841</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1,860</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1,870</t>
+          <t>646</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="69" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-06</t>
+          <t>Views_2026-10-07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-07</t>
+          <t>Views_2026-10-08</t>
         </is>
       </c>
     </row>
@@ -497,83 +497,194 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>598</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>605</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AB5Tw2Yd4qE</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>289</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TH331d5OGVs</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>646</t>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1,320</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1,332</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-07</t>
+          <t>Views_2026-10-08</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-08</t>
+          <t>Views_2026-10-09</t>
         </is>
       </c>
     </row>
@@ -497,76 +497,76 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>605</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>608</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>69</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,34 +576,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>182</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>183</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TH331d5OGVs</t>
+          <t>AB5Tw2Yd4qE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
+          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
+          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,34 +613,34 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>nSSLusuBoC8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,41 +650,78 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>TH331d5OGVs</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1,320</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1,332</t>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1,008</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -465,263 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-08</t>
+          <t>Views_2026-10-09</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>q8sgDwcuE0A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>You OFFER First, So They Stop ASKING</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>5u_0LFn95ec</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AB5Tw2Yd4qE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-01-04</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>nSSLusuBoC8</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TH331d5OGVs</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1,008</t>
+          <t>Views_2026-10-10</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -465,12 +465,78 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-09</t>
+          <t>Views_2026-10-10</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-10</t>
+          <t>Views_2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>611</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -465,78 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-10</t>
+          <t>Views_2026-10-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>611</t>
+          <t>Views_2026-10-12</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -465,12 +465,115 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-11</t>
+          <t>Views_2026-10-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-12</t>
+          <t>Views_2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>y_HfwluuNI8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>You Said NO — Then You Ruined It</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>717</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -465,115 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-12</t>
+          <t>Views_2026-10-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>y_HfwluuNI8</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>You Said NO — Then You Ruined It</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>717</t>
+          <t>Views_2026-10-15</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -465,12 +465,115 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-14</t>
+          <t>Views_2026-10-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-15</t>
+          <t>Views_2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hzoRggV72as</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>656</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-15</t>
+          <t>Views_2026-10-16</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-16</t>
+          <t>Views_2026-10-17</t>
         </is>
       </c>
     </row>
@@ -497,41 +497,33 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>616</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>617</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hzoRggV72as</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>1</t>
@@ -539,41 +531,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>616</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>656</t>
+          <t>617</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-16</t>
+          <t>Views_2026-10-17</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-17</t>
+          <t>Views_2026-10-18</t>
         </is>
       </c>
     </row>
@@ -497,46 +497,157 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>617</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>619</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>nCKMh-qdDTk</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pYH8XAZ8h0A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>617</t>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1,696</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1,701</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="61" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-17</t>
+          <t>Views_2026-10-18</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-18</t>
+          <t>Views_2026-10-19</t>
         </is>
       </c>
     </row>
@@ -497,76 +497,76 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>619</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>624</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>105</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,34 +576,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>184</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>A0x6fkcrix4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,41 +613,78 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>119</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2Hqop6uU8PY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>“So Sensitive?” Here’s the Calm Stoic Response That Ends It</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2Hqop6uU8PY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1,696</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1,701</t>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1,080</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1,090</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="61" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-18</t>
+          <t>Views_2026-10-19</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-19</t>
+          <t>Views_2026-10-20</t>
         </is>
       </c>
     </row>
@@ -497,39 +497,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>624</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>634</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>93</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,34 +576,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,78 +613,41 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>71</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2Hqop6uU8PY</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>“So Sensitive?” Here’s the Calm Stoic Response That Ends It</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=2Hqop6uU8PY</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>879</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1,080</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1,090</t>
+          <t>893</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-19</t>
+          <t>Views_2026-10-20</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-20</t>
+          <t>Views_2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>The Calm Response That Stops Rude People Fast</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>217</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>634</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>636</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,78 +576,41 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>882</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>879</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>893</t>
+          <t>891</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -429,7 +429,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-20</t>
+          <t>Views_2026-10-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-21</t>
+          <t>Views_2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>qUd0X0Wn4-s</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>636</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>638</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>2OilqvW_HzY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>291</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>293</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>159</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>160</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>1,086</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>1,091</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-21</t>
+          <t>Views_2026-10-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-22</t>
+          <t>Views_2026-10-24</t>
         </is>
       </c>
     </row>
@@ -497,76 +497,76 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>638</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>642</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,41 +576,78 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>71</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1,086</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1,091</t>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1,095</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1,102</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-22</t>
+          <t>Views_2026-10-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-24</t>
+          <t>Views_2026-10-25</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>160</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>161</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,115 +539,41 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>642</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>643</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>802</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2OilqvW_HzY</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1,095</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1,102</t>
+          <t>804</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-24</t>
+          <t>Views_2026-10-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-25</t>
+          <t>Views_2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,34 +502,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>217</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,41 +539,78 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>98</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>804</t>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>960</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-25</t>
+          <t>Views_2026-10-26</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-26</t>
+          <t>Views_2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>644</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>647</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>403</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>BypRuE0bqNg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>If They Don’t Respect You, Walk Away (5 Seneca Rules)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=BypRuE0bqNg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,41 +576,78 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>IKtI1Kc9YC8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>You’re Not Kind — You’re Being Used (5 Stoic Truths)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IKtI1Kc9YC8</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>960</t>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1,210</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1,216</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-26</t>
+          <t>Views_2026-10-27</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-27</t>
+          <t>Views_2026-10-28</t>
         </is>
       </c>
     </row>
@@ -497,76 +497,76 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>647</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>649</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>TH331d5OGVs</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BypRuE0bqNg</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>If They Don’t Respect You, Walk Away (5 Seneca Rules)</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BypRuE0bqNg</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,34 +576,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKtI1Kc9YC8</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>You’re Not Kind — You’re Being Used (5 Stoic Truths)</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IKtI1Kc9YC8</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,41 +613,115 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>8fhVxgOWZ84</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1,210</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1,216</t>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1,068</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1,076</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-27</t>
+          <t>Views_2026-10-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-28</t>
+          <t>Views_2026-10-29</t>
         </is>
       </c>
     </row>
@@ -502,226 +502,78 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>649</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>651</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TH331d5OGVs</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>73</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>722</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>lIx_B-vwa8g</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>8fhVxgOWZ84</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1,068</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1,076</t>
+          <t>725</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-28</t>
+          <t>Views_2026-10-29</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-10-29</t>
+          <t>Views_2026-10-31</t>
         </is>
       </c>
     </row>
@@ -497,39 +497,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>651</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>658</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>fMZNVUsnWlw</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>Low Self-Worth: 3 Stoic Rules To Rebuild Your Inner Value</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=fMZNVUsnWlw</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>704</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>712</t>
         </is>
       </c>
     </row>
